--- a/data/trans_camb/P0902-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P0902-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 2,27</t>
+          <t>-4,89; 1,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 4,2</t>
+          <t>-3,26; 3,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 4,18</t>
+          <t>-3,05; 3,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 5,14</t>
+          <t>-5,31; 5,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 4,08</t>
+          <t>-5,57; 4,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 5,21</t>
+          <t>-4,13; 5,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,73</t>
+          <t>-3,56; 2,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,17</t>
+          <t>-2,73; 3,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,65</t>
+          <t>-1,86; 3,68</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-53,71; 43,29</t>
+          <t>-55,49; 33,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 76,31</t>
+          <t>-37,3; 72,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,06; 76,71</t>
+          <t>-33,09; 74,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 54,25</t>
+          <t>-38,13; 60,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,53; 44,61</t>
+          <t>-40,13; 53,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,64; 58,3</t>
+          <t>-27,64; 57,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 37,81</t>
+          <t>-34,7; 30,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 43,22</t>
+          <t>-26,14; 47,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 49,34</t>
+          <t>-17,45; 53,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 9,28</t>
+          <t>1,01; 9,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 3,62</t>
+          <t>-2,48; 3,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 7,51</t>
+          <t>0,13; 7,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 6,74</t>
+          <t>-2,77; 6,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 4,96</t>
+          <t>-3,9; 5,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 7,61</t>
+          <t>-0,17; 8,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,65</t>
+          <t>0,33; 6,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,12</t>
+          <t>-1,95; 3,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,78</t>
+          <t>1,42; 6,64</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,21; 255,06</t>
+          <t>13,24; 279,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,49; 108,32</t>
+          <t>-39,93; 129,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 215,63</t>
+          <t>1,46; 239,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,33; 94,55</t>
+          <t>-24,89; 95,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,49; 72,19</t>
+          <t>-35,5; 70,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 108,31</t>
+          <t>-3,25; 120,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 114,72</t>
+          <t>3,18; 108,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,06; 52,5</t>
+          <t>-23,67; 57,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 125,2</t>
+          <t>14,68; 116,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 10,04</t>
+          <t>2,1; 9,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,78</t>
+          <t>-2,08; 4,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 8,81</t>
+          <t>-5,75; 8,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 8,66</t>
+          <t>-6,75; 8,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 12,55</t>
+          <t>-4,89; 12,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 11,49</t>
+          <t>-3,63; 13,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,15</t>
+          <t>1,07; 8,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 5,4</t>
+          <t>-1,52; 5,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 8,29</t>
+          <t>-6,45; 7,92</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,87; 172,74</t>
+          <t>21,45; 164,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,04; 81,48</t>
+          <t>-22,9; 81,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,1; 124,25</t>
+          <t>-61,19; 120,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 60,87</t>
+          <t>-29,86; 63,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 85,87</t>
+          <t>-23,49; 86,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 77,25</t>
+          <t>-16,38; 89,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,7; 94,97</t>
+          <t>8,21; 94,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 61,32</t>
+          <t>-12,98; 59,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,59; 88,19</t>
+          <t>-55,13; 80,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,46</t>
+          <t>-0,03; 5,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,05</t>
+          <t>-2,01; 2,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 8,59</t>
+          <t>2,81; 8,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 6,35</t>
+          <t>-0,49; 6,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,2</t>
+          <t>-2,78; 4,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 4,8</t>
+          <t>-7,29; 4,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,89</t>
+          <t>0,77; 4,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,7</t>
+          <t>-1,29; 2,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,96</t>
+          <t>-1,64; 5,84</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 61,85</t>
+          <t>-0,41; 60,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 33,06</t>
+          <t>-17,48; 32,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,54; 94,22</t>
+          <t>23,69; 94,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 57,97</t>
+          <t>-4,0; 62,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 41,39</t>
+          <t>-19,5; 40,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-45,34; 42,38</t>
+          <t>-51,79; 41,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,91; 48,38</t>
+          <t>6,15; 48,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 27,84</t>
+          <t>-10,52; 26,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 58,44</t>
+          <t>-10,83; 56,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 6,32</t>
+          <t>-2,2; 6,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 7,09</t>
+          <t>-1,29; 6,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,09; 12,09</t>
+          <t>2,8; 12,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,38; 17,33</t>
+          <t>8,0; 17,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,34; 12,99</t>
+          <t>4,24; 13,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,39; 13,72</t>
+          <t>2,47; 13,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,03; 11,58</t>
+          <t>5,37; 11,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,88</t>
+          <t>2,71; 9,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,38; 12,12</t>
+          <t>3,9; 12,06</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 79,48</t>
+          <t>-18,16; 81,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 89,43</t>
+          <t>-9,92; 88,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23,9; 144,78</t>
+          <t>18,62; 146,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51,23; 143,23</t>
+          <t>47,68; 139,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>24,85; 103,28</t>
+          <t>24,7; 108,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,26; 108,42</t>
+          <t>16,79; 116,63</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,07; 99,92</t>
+          <t>34,67; 106,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18,56; 77,13</t>
+          <t>17,7; 81,88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>31,5; 105,66</t>
+          <t>28,84; 106,55</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 3,73</t>
+          <t>-2,4; 3,91</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,99</t>
+          <t>-4,33; 0,83</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,11</t>
+          <t>-3,45; 2,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,96; 8,7</t>
+          <t>2,18; 9,1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,44; 7,42</t>
+          <t>0,51; 7,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,33; 10,18</t>
+          <t>3,65; 10,4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,5; 7,12</t>
+          <t>1,67; 7,35</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 5,56</t>
+          <t>-0,09; 5,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,08</t>
+          <t>1,65; 7,4</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-59,77; 187,33</t>
+          <t>-55,51; 211,1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-90,69; 72,62</t>
+          <t>-89,81; 90,92</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-73,35; 136,47</t>
+          <t>-71,93; 159,01</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10,08; 52,06</t>
+          <t>11,48; 57,27</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,82; 44,69</t>
+          <t>2,72; 46,6</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,35; 62,75</t>
+          <t>19,01; 64,98</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,55; 52,66</t>
+          <t>10,0; 53,8</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 40,11</t>
+          <t>-0,09; 42,91</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9,63; 53,05</t>
+          <t>10,69; 55,14</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,3</t>
+          <t>1,31; 4,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,55</t>
+          <t>-0,2; 2,46</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,38</t>
+          <t>0,94; 5,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,13</t>
+          <t>3,43; 7,21</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,95</t>
+          <t>1,18; 4,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,7</t>
+          <t>0,36; 5,83</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,35</t>
+          <t>3,0; 5,3</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,29</t>
+          <t>1,02; 3,39</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,18</t>
+          <t>1,88; 5,27</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>15,23; 56,28</t>
+          <t>14,54; 57,61</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 34,02</t>
+          <t>-2,48; 32,89</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9,38; 70,95</t>
+          <t>11,77; 72,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22,99; 52,17</t>
+          <t>21,92; 52,48</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,81; 35,54</t>
+          <t>7,67; 34,22</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,57; 40,88</t>
+          <t>2,92; 41,89</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,61; 48,88</t>
+          <t>24,93; 49,39</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8,61; 30,79</t>
+          <t>8,64; 31,51</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>13,64; 46,86</t>
+          <t>15,86; 47,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P0902-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P0902-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>0,95</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 1,78</t>
+          <t>-5,23; 1,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 3,95</t>
+          <t>-3,34; 4,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 3,92</t>
+          <t>-2,95; 3,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 5,39</t>
+          <t>-4,95; 5,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 4,7</t>
+          <t>-5,79; 4,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 5,09</t>
+          <t>-3,67; 4,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 2,26</t>
+          <t>-3,33; 2,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,51</t>
+          <t>-2,71; 3,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,68</t>
+          <t>-1,78; 3,61</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,49; 33,84</t>
+          <t>-54,8; 33,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 72,7</t>
+          <t>-37,99; 79,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 74,39</t>
+          <t>-32,07; 69,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,13; 60,43</t>
+          <t>-36,39; 65,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 53,59</t>
+          <t>-42,39; 56,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 57,32</t>
+          <t>-25,55; 59,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,7; 30,02</t>
+          <t>-32,16; 31,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 47,34</t>
+          <t>-27,06; 43,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 53,81</t>
+          <t>-16,7; 50,61</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>3,87</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>4,62</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,9</t>
+          <t>4,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,35</t>
+          <t>1,29; 9,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,97</t>
+          <t>-2,76; 3,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 7,64</t>
+          <t>0,13; 7,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 6,5</t>
+          <t>-3,3; 6,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 5,02</t>
+          <t>-3,65; 5,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 8,23</t>
+          <t>0,5; 8,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 6,4</t>
+          <t>0,63; 6,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 3,39</t>
+          <t>-2,25; 3,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,64</t>
+          <t>1,6; 6,64</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>57,5%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,24; 279,74</t>
+          <t>16,51; 263,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,93; 129,83</t>
+          <t>-39,76; 116,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 239,14</t>
+          <t>-0,16; 214,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,89; 95,21</t>
+          <t>-31,33; 95,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 70,18</t>
+          <t>-33,41; 78,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 120,62</t>
+          <t>4,15; 116,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 108,28</t>
+          <t>7,81; 114,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 57,15</t>
+          <t>-28,01; 60,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,68; 116,1</t>
+          <t>18,18; 121,32</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>3,85</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>6,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 9,99</t>
+          <t>2,15; 10,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 4,86</t>
+          <t>-2,41; 4,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 8,6</t>
+          <t>2,68; 10,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 8,87</t>
+          <t>-6,47; 9,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 12,72</t>
+          <t>-5,13; 12,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 13,18</t>
+          <t>-4,42; 12,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 8,23</t>
+          <t>1,89; 8,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 5,24</t>
+          <t>-1,16; 5,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 7,92</t>
+          <t>2,97; 9,92</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,45; 164,94</t>
+          <t>23,17; 164,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 81,56</t>
+          <t>-26,55; 74,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,19; 120,34</t>
+          <t>31,16; 180,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,86; 63,02</t>
+          <t>-28,76; 65,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 86,97</t>
+          <t>-23,29; 91,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 89,64</t>
+          <t>-18,7; 83,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,21; 94,08</t>
+          <t>15,19; 97,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 59,33</t>
+          <t>-10,5; 64,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 80,62</t>
+          <t>25,54; 120,28</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,66</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>3,97</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>4,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 5,5</t>
+          <t>-0,01; 5,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,96</t>
+          <t>-2,13; 3,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,51</t>
+          <t>2,83; 8,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 6,51</t>
+          <t>-0,73; 6,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 4,22</t>
+          <t>-2,82; 3,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 4,73</t>
+          <t>0,29; 7,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,98</t>
+          <t>0,61; 5,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,68</t>
+          <t>-1,24; 2,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 5,84</t>
+          <t>3,09; 7,19</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>45,48%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 60,45</t>
+          <t>-1,56; 57,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 32,98</t>
+          <t>-18,96; 33,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,69; 94,0</t>
+          <t>22,75; 89,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 62,9</t>
+          <t>-5,11; 61,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,5; 40,8</t>
+          <t>-19,41; 37,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,79; 41,79</t>
+          <t>1,73; 69,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,15; 48,95</t>
+          <t>4,73; 49,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 26,58</t>
+          <t>-10,04; 28,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 56,02</t>
+          <t>25,84; 72,1</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,54</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,95</t>
+          <t>11,13</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,53</t>
+          <t>8,93</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 6,34</t>
+          <t>-2,73; 5,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 6,97</t>
+          <t>-0,81; 7,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,8; 12,14</t>
+          <t>1,45; 10,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,0; 17,15</t>
+          <t>8,26; 17,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,24; 13,31</t>
+          <t>4,21; 12,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 13,92</t>
+          <t>7,38; 14,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,37; 11,92</t>
+          <t>4,88; 11,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,71; 9,09</t>
+          <t>2,6; 8,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,9; 12,06</t>
+          <t>6,11; 11,72</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>68,39%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 81,52</t>
+          <t>-20,63; 73,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 88,23</t>
+          <t>-6,34; 100,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18,62; 146,37</t>
+          <t>9,83; 139,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47,68; 139,0</t>
+          <t>47,05; 137,4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>24,7; 108,27</t>
+          <t>24,58; 101,81</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,79; 116,63</t>
+          <t>39,67; 118,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,67; 106,38</t>
+          <t>32,43; 104,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>17,7; 81,88</t>
+          <t>17,94; 78,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>28,84; 106,55</t>
+          <t>40,09; 105,55</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>-0,7</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>6,53</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>4,56</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,91</t>
+          <t>-2,58; 3,86</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,83</t>
+          <t>-4,24; 1,16</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 2,4</t>
+          <t>-3,37; 2,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,1</t>
+          <t>2,15; 8,72</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,51; 7,53</t>
+          <t>0,77; 7,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,65; 10,4</t>
+          <t>3,11; 9,72</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,35</t>
+          <t>1,76; 7,19</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 5,75</t>
+          <t>-0,65; 5,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,4</t>
+          <t>1,83; 7,29</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-20,97%</t>
+          <t>-21,89%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-55,51; 211,1</t>
+          <t>-58,78; 197,76</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-89,81; 90,92</t>
+          <t>-90,14; 79,75</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-71,93; 159,01</t>
+          <t>-73,62; 129,19</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11,48; 57,27</t>
+          <t>11,26; 54,63</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,72; 46,6</t>
+          <t>4,05; 46,39</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,01; 64,98</t>
+          <t>16,51; 62,55</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,0; 53,8</t>
+          <t>10,51; 51,83</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 42,91</t>
+          <t>-4,15; 39,74</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>10,69; 55,14</t>
+          <t>11,05; 53,24</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>5,22</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>4,82</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,33</t>
+          <t>1,4; 4,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,46</t>
+          <t>-0,19; 2,56</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,42</t>
+          <t>3,01; 5,91</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,21</t>
+          <t>3,47; 7,26</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,76</t>
+          <t>1,29; 4,9</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,83</t>
+          <t>3,64; 6,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,3</t>
+          <t>2,92; 5,28</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,39</t>
+          <t>0,97; 3,21</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,27</t>
+          <t>3,6; 5,91</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>14,54; 57,61</t>
+          <t>15,56; 57,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 32,89</t>
+          <t>-2,11; 33,87</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11,77; 72,52</t>
+          <t>34,31; 80,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21,92; 52,48</t>
+          <t>22,55; 52,57</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,67; 34,22</t>
+          <t>8,36; 36,51</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,92; 41,89</t>
+          <t>23,29; 49,9</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,93; 49,39</t>
+          <t>23,63; 48,29</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8,64; 31,51</t>
+          <t>8,26; 30,09</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>15,86; 47,75</t>
+          <t>29,82; 54,41</t>
         </is>
       </c>
     </row>
